--- a/data/2a_causal_estimates_papers/corrected/manzan_gas.xlsx
+++ b/data/2a_causal_estimates_papers/corrected/manzan_gas.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarah/Library/CloudStorage/Dropbox-MIT/Regulation/Replication Package/2a_causal_estimates_papers/corrected/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jgk422\Opportunity Insights Dropbox\Jack Kelly\miscellany\JK_ed_wrapper_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9767062D-9FF6-0542-A582-050176F4C75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA736FE-9A8B-463F-8081-ABC227FDF550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3160" yWindow="3340" windowWidth="25120" windowHeight="10780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3165" yWindow="3330" windowWidth="25125" windowHeight="10785" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="wrapper_ready" sheetId="1" r:id="rId1"/>
     <sheet name="raw_data" sheetId="2" r:id="rId2"/>
     <sheet name="calculations" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="210" uniqueCount="39">
   <si>
     <t>estimate</t>
   </si>
@@ -79,12 +79,21 @@
     <t>source</t>
   </si>
   <si>
+    <t>pub_bias</t>
+  </si>
+  <si>
+    <t>expected_sign</t>
+  </si>
+  <si>
     <t>Link to PDF:</t>
   </si>
   <si>
     <t>Downloaded:</t>
   </si>
   <si>
+    <t>Jack</t>
+  </si>
+  <si>
     <t>Point of contact:</t>
   </si>
   <si>
@@ -94,6 +103,9 @@
     <t>Notes:</t>
   </si>
   <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S254243512200410X#appsec2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Source Info </t>
   </si>
   <si>
@@ -112,6 +124,9 @@
     <t>Demand elasticity of solar photovoltaics</t>
   </si>
   <si>
+    <t>Click on "Supplemental information" and Download "Document S2. Article plus supplemental information" to get the version with Table S20</t>
+  </si>
+  <si>
     <t>Table S20 Column 1 Rows 1-2 , p.97</t>
   </si>
   <si>
@@ -125,6 +140,9 @@
   </si>
   <si>
     <t>e_demand_gas</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/doi/full/10.1080/07474930903562320</t>
   </si>
   <si>
     <t>Table 4 Column 7-8 Row 1, p.460</t>
@@ -139,8 +157,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,6 +310,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -342,19 +368,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79995117038483843"/>
+        <fgColor theme="4" tint="0.79998168889431"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59996337778862885"/>
+        <fgColor theme="4" tint="0.5999938962981"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -365,19 +391,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79995117038483843"/>
+        <fgColor theme="5" tint="0.79998168889431"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59996337778862885"/>
+        <fgColor theme="5" tint="0.5999938962981"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -388,19 +414,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79995117038483843"/>
+        <fgColor theme="6" tint="0.79998168889431"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59996337778862885"/>
+        <fgColor theme="6" tint="0.5999938962981"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor theme="6" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -411,19 +437,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79995117038483843"/>
+        <fgColor theme="7" tint="0.79998168889431"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59996337778862885"/>
+        <fgColor theme="7" tint="0.5999938962981"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -434,19 +460,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79995117038483843"/>
+        <fgColor theme="8" tint="0.79998168889431"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59996337778862885"/>
+        <fgColor theme="8" tint="0.5999938962981"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
+        <fgColor theme="8" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -457,19 +483,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="9" tint="0.79998168889431"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59996337778862885"/>
+        <fgColor theme="9" tint="0.5999938962981"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.39997558519242"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -496,7 +522,7 @@
       <right/>
       <top/>
       <bottom style="thick">
-        <color theme="4" tint="0.49995422223578601"/>
+        <color theme="4" tint="0.49998474074526"/>
       </bottom>
       <diagonal/>
     </border>
@@ -505,7 +531,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.39997558519242"/>
       </bottom>
       <diagonal/>
     </border>
@@ -589,121 +615,125 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="16" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="16" applyFont="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="16" applyNumberFormat="true" applyAlignment="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="16" applyAlignment="true"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyAlignment="true"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="43">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="true"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="true"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="true"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="true"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="true"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="true"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="true"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="true"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="true"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="true"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="true"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="true"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="true"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="true"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="true"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="true"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="true"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="true"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="true"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="true"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="true"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="true"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="true"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="true"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="true"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="true"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="true"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="true"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="true"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="true"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="true"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="true"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="true"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="true"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="true"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="true"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="true"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="true"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="true"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="true"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -719,7 +749,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -870,7 +900,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -894,9 +924,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -920,7 +950,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -955,7 +985,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -973,7 +1003,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -998,7 +1028,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1034,11 +1064,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1076,13 +1106,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <f>raw_data!B3</f>
-        <v>-0.34247368574142456</v>
+        <v>-0.35499999999999998</v>
       </c>
       <c r="C2">
         <f>raw_data!C3</f>
@@ -1095,13 +1125,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3">
         <f>calculations!C2</f>
-        <v>-0.42100000381469727</v>
+        <v>-0.42099999999999999</v>
       </c>
       <c r="C3">
         <f>raw_data!C14</f>
@@ -1117,48 +1147,47 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.6640625" style="2"/>
-    <col min="8" max="8" width="12" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" style="2"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="16384" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="27.7265625" style="2" customWidth="true"/>
+    <col min="2" max="2" width="9.81640625" style="2" bestFit="true" customWidth="true"/>
+    <col min="3" max="7" width="8.7265625" style="2"/>
+    <col min="8" max="8" width="12" style="2" customWidth="true"/>
+    <col min="9" max="9" width="8.7265625" style="2"/>
+    <col min="11" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+        <v>37</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
       <c r="E1" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
       <c r="J1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1168,247 +1197,247 @@
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="6" t="s">
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="7">
+        <v>28</v>
+      </c>
+      <c r="B3" s="11">
         <v>-0.34247368574142456</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="11">
         <v>0.11700000000000001</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="11"/>
       <c r="E3" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="7">
+        <v>38</v>
+      </c>
+      <c r="H3" s="11">
         <v>1</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="11">
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
       <c r="J4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
       <c r="J5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
       <c r="E6" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
       <c r="J6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
       <c r="E10" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
       <c r="J10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
       <c r="E11" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
       <c r="J11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
       <c r="J12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
@@ -1418,437 +1447,437 @@
       <c r="G13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="6" t="s">
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="11">
+        <v>0.42100000381469727</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0.063</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="11">
+        <v>1</v>
+      </c>
+      <c r="I14" s="11">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="7">
-        <v>0.42100000381469727</v>
-      </c>
-      <c r="C14" s="7">
-        <v>6.3E-2</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H14" s="7">
-        <v>1</v>
-      </c>
-      <c r="I14" s="7">
-        <v>1</v>
-      </c>
-      <c r="J14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
       <c r="E18" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
       <c r="J18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+        <v>19</v>
+      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
       <c r="E19" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
       <c r="J19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+        <v>21</v>
+      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
       <c r="E20" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
       <c r="J20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
       <c r="E21" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="11"/>
       <c r="J21" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
       <c r="E22" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="11"/>
       <c r="J22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
       <c r="E23" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
       <c r="E24" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
       <c r="J24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
       <c r="E25" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
       <c r="J25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
       <c r="E26" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
       <c r="J26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
       <c r="E27" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
       <c r="J27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
       <c r="E28" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
       <c r="J28" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
       <c r="E29" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
       <c r="J29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
       <c r="E30" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
+        <v>38</v>
+      </c>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
       <c r="J30" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B17" r:id="rId1" location="appsec2" display="https://www.sciencedirect.com/science/article/pii/S254243512200410X - appsec2" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="B17" r:id="rId1" location="appsec2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="45.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="2"/>
+    <col min="1" max="1" width="24.54296875" style="1" customWidth="true"/>
+    <col min="2" max="2" width="45.7265625" style="1" customWidth="true"/>
+    <col min="3" max="3" width="10.90625" style="1" customWidth="true"/>
+    <col min="4" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2">
         <f>-raw_data!B14</f>
-        <v>-0.42100000381469727</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>-0.42099999999999999</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
